--- a/isms-core-framework/A.8-technological-controls/isms-a.8.15-logging/WKBK/90_workbooks/ISMS-IMP-A.8.15.1_Log_Source_Inventory_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.15-logging/WKBK/90_workbooks/ISMS-IMP-A.8.15.1_Log_Source_Inventory_20260208.xlsx
@@ -6456,7 +6456,7 @@
       </c>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>PCI DSS, GDPR</t>
+          <t>PCI DSS v4.0.1, GDPR</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr">
